--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72764887-92EB-4105-8C57-DAC59B97E0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEC4C98-09EB-4A72-B928-46EF777001B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8835" yWindow="360" windowWidth="20295" windowHeight="12150" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="BVS-psgr-LDVs" sheetId="2" r:id="rId5"/>
     <sheet name="BVS-psgr-HDVs" sheetId="101" r:id="rId6"/>
     <sheet name="BVS-psgr-aircraft" sheetId="105" r:id="rId7"/>
-    <sheet name="BVS-psgr-rail" sheetId="104" r:id="rId8"/>
+    <sheet name="BVP-psgr-rail" sheetId="104" r:id="rId8"/>
     <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId9"/>
     <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId10"/>
     <sheet name="frgt" sheetId="106" r:id="rId11"/>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="123">
   <si>
     <t>Sources:</t>
   </si>
@@ -515,9 +515,6 @@
   <si>
     <t>Frgt LDV (2012 $)</t>
   </si>
-  <si>
-    <t>took out IRA</t>
-  </si>
 </sst>
 </file>
 
@@ -671,7 +668,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,12 +702,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,7 +827,7 @@
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -909,7 +900,6 @@
     <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="34">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1314,17 +1304,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="69.28515625" customWidth="1"/>
+    <col min="2" max="2" width="69.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1332,47 +1322,47 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" s="19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" s="3"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B28" s="4"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
     </row>
   </sheetData>
@@ -1388,12 +1378,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1488,7 +1478,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1583,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1678,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1773,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1868,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1963,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2058,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2164,7 +2154,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2176,12 +2166,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -2276,7 +2266,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2299,25 +2289,32 @@
         <v>9098.157067904207</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <f>'Commercial Vehicles'!E10</f>
+        <v>8900.5394373583313</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <f>'Commercial Vehicles'!F10</f>
+        <v>8762.1955571514172</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <f>'Commercial Vehicles'!G10</f>
+        <v>8574.638599520662</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <f>'Commercial Vehicles'!H10</f>
+        <v>8327.2183891071436</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <f>'Commercial Vehicles'!I10</f>
+        <v>8038.2687173078502</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <f>'Commercial Vehicles'!J10</f>
+        <v>7772.0490463949827</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <f>'Commercial Vehicles'!K10</f>
+        <v>7566.1942040579743</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -2374,7 +2371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2469,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2564,7 +2561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2659,7 +2656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2683,31 +2680,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8900.5394373583313</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8762.1955571514172</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8574.638599520662</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8327.2183891071436</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8038.2687173078502</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7772.0490463949827</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7566.1942040579743</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2764,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2859,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2883,31 +2880,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8900.5394373583313</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8762.1955571514172</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8574.638599520662</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8327.2183891071436</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8038.2687173078502</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7772.0490463949827</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7566.1942040579743</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2976,13 +2973,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3077,7 +3074,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3100,82 +3097,89 @@
         <v>28423.922562347398</v>
       </c>
       <c r="G2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14</f>
+        <v>27596.041322667374</v>
       </c>
       <c r="H2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14</f>
+        <v>26792.273128803277</v>
       </c>
       <c r="I2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14</f>
+        <v>26011.915659032311</v>
       </c>
       <c r="J2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14</f>
+        <v>25254.287047604183</v>
       </c>
       <c r="K2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14</f>
+        <v>24518.725288936101</v>
       </c>
       <c r="L2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14</f>
+        <v>23804.587659161265</v>
       </c>
       <c r="M2" s="51">
-        <v>0</v>
-      </c>
-      <c r="N2" s="51">
-        <v>0</v>
-      </c>
-      <c r="O2" s="51">
-        <v>0</v>
-      </c>
-      <c r="P2" s="51">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="51">
-        <v>0</v>
-      </c>
-      <c r="R2" s="51">
-        <v>0</v>
-      </c>
-      <c r="S2" s="51">
-        <v>0</v>
-      </c>
-      <c r="T2" s="51">
-        <v>0</v>
-      </c>
-      <c r="U2" s="51">
-        <v>0</v>
-      </c>
-      <c r="V2" s="51">
-        <v>0</v>
-      </c>
-      <c r="W2" s="51">
-        <v>0</v>
-      </c>
-      <c r="X2" s="51">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="51">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14</f>
+        <v>23111.250154525496</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3270,7 +3274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3365,7 +3369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3460,7 +3464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3484,31 +3488,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27596.041322667374</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26792.273128803277</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26011.915659032311</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25254.287047604183</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24518.725288936101</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23804.587659161265</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23111.250154525496</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3565,7 +3569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3660,7 +3664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3684,31 +3688,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>27596.041322667374</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26792.273128803277</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26011.915659032311</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25254.287047604183</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24518.725288936101</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23804.587659161265</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23111.250154525496</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3776,12 +3780,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3876,7 +3880,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3971,7 +3975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4066,7 +4070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4161,7 +4165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4256,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4351,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4446,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4552,12 +4556,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -4652,7 +4656,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4747,7 +4751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4842,7 +4846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4937,7 +4941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5032,7 +5036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5127,7 +5131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5222,7 +5226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5328,12 +5332,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5428,7 +5432,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5523,7 +5527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5618,7 +5622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5713,7 +5717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5808,7 +5812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5903,7 +5907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5998,7 +6002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6104,12 +6108,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -6204,7 +6208,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6299,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6394,7 +6398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6489,7 +6493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6584,7 +6588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6679,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6774,7 +6778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6877,34 +6881,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8A3CC6-8591-4A07-9E4B-1DE39D29E87F}">
   <dimension ref="A1:AF107"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="45.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="4" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2021</v>
       </c>
@@ -6996,7 +7000,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
@@ -7091,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
@@ -7186,34 +7190,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>119</v>
       </c>
       <c r="B12" s="7"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>13</v>
       </c>
@@ -7222,7 +7226,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>15</v>
       </c>
@@ -7231,13 +7235,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="8"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>18</v>
       </c>
@@ -7281,7 +7285,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="36" t="s">
         <v>21</v>
       </c>
@@ -7321,7 +7325,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="36" t="s">
         <v>23</v>
       </c>
@@ -7369,7 +7373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
@@ -7411,7 +7415,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>26</v>
       </c>
@@ -7457,7 +7461,7 @@
       </c>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>27</v>
       </c>
@@ -7494,7 +7498,7 @@
       <c r="L21" s="10"/>
       <c r="M21" s="11"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>29</v>
       </c>
@@ -7537,7 +7541,7 @@
       </c>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>30</v>
       </c>
@@ -7574,7 +7578,7 @@
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
     </row>
-    <row r="24" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>31</v>
       </c>
@@ -7610,7 +7614,7 @@
       </c>
       <c r="R24" s="12"/>
     </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>90</v>
       </c>
@@ -7645,7 +7649,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
@@ -7677,7 +7681,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
@@ -7709,7 +7713,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>92</v>
       </c>
@@ -7745,7 +7749,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>94</v>
       </c>
@@ -7777,7 +7781,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>34</v>
       </c>
@@ -7812,7 +7816,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
@@ -7857,7 +7861,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>36</v>
       </c>
@@ -7892,7 +7896,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>37</v>
       </c>
@@ -7924,7 +7928,7 @@
       </c>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>38</v>
       </c>
@@ -7932,11 +7936,11 @@
         <v>329.5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
     </row>
-    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>99</v>
       </c>
@@ -7974,7 +7978,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="36" t="s">
         <v>21</v>
       </c>
@@ -8014,7 +8018,7 @@
       </c>
       <c r="L37"/>
     </row>
-    <row r="38" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="36" t="s">
         <v>23</v>
       </c>
@@ -8054,7 +8058,7 @@
       </c>
       <c r="L38"/>
     </row>
-    <row r="39" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>25</v>
       </c>
@@ -8088,7 +8092,7 @@
       </c>
       <c r="L39"/>
     </row>
-    <row r="40" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>26</v>
       </c>
@@ -8128,7 +8132,7 @@
       </c>
       <c r="L40"/>
     </row>
-    <row r="41" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>27</v>
       </c>
@@ -8161,7 +8165,7 @@
       </c>
       <c r="L41"/>
     </row>
-    <row r="42" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>29</v>
       </c>
@@ -8198,7 +8202,7 @@
       </c>
       <c r="L42"/>
     </row>
-    <row r="43" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>30</v>
       </c>
@@ -8231,7 +8235,7 @@
       </c>
       <c r="L43"/>
     </row>
-    <row r="44" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>31</v>
       </c>
@@ -8264,7 +8268,7 @@
       </c>
       <c r="L44"/>
     </row>
-    <row r="45" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>90</v>
       </c>
@@ -8297,7 +8301,7 @@
       </c>
       <c r="L45"/>
     </row>
-    <row r="46" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>32</v>
       </c>
@@ -8330,7 +8334,7 @@
       </c>
       <c r="L46"/>
     </row>
-    <row r="47" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>33</v>
       </c>
@@ -8364,7 +8368,7 @@
       </c>
       <c r="L47"/>
     </row>
-    <row r="48" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>92</v>
       </c>
@@ -8398,7 +8402,7 @@
       </c>
       <c r="L48"/>
     </row>
-    <row r="49" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>94</v>
       </c>
@@ -8431,7 +8435,7 @@
       </c>
       <c r="L49"/>
     </row>
-    <row r="50" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>34</v>
       </c>
@@ -8464,7 +8468,7 @@
       </c>
       <c r="L50"/>
     </row>
-    <row r="51" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>35</v>
       </c>
@@ -8504,7 +8508,7 @@
       </c>
       <c r="L51"/>
     </row>
-    <row r="52" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>36</v>
       </c>
@@ -8537,7 +8541,7 @@
       </c>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>37</v>
       </c>
@@ -8569,7 +8573,7 @@
       </c>
       <c r="L53"/>
     </row>
-    <row r="54" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>38</v>
       </c>
@@ -8578,11 +8582,11 @@
       </c>
       <c r="L54"/>
     </row>
-    <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
     </row>
-    <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -8594,13 +8598,13 @@
       <c r="I56" s="8"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" s="14"/>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>44</v>
       </c>
@@ -8608,15 +8612,15 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.35">
       <c r="C62">
         <v>2021</v>
       </c>
@@ -8708,7 +8712,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>40</v>
       </c>
@@ -8818,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>41</v>
       </c>
@@ -8928,18 +8932,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H66" s="52" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.35">
       <c r="C67">
         <v>2021</v>
       </c>
@@ -9031,17 +9032,17 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5">
-        <f>B5+C63</f>
+        <f t="shared" ref="C68:AF68" si="8">B5+C63</f>
         <v>1930.7404811231229</v>
       </c>
       <c r="D68" s="5">
-        <f t="shared" ref="D68:G68" si="8">C5+D63</f>
+        <f t="shared" si="8"/>
         <v>1599.8025784220101</v>
       </c>
       <c r="E68" s="5">
@@ -9049,7 +9050,7 @@
         <v>5130.1015918271351</v>
       </c>
       <c r="F68" s="5">
-        <f>E5+F63</f>
+        <f t="shared" si="8"/>
         <v>3819.9265877142789</v>
       </c>
       <c r="G68" s="5">
@@ -9057,107 +9058,107 @@
         <v>3565.6148024975096</v>
       </c>
       <c r="H68" s="5">
-        <f>H63</f>
-        <v>194.10400882122519</v>
+        <f t="shared" si="8"/>
+        <v>3312.3286898445285</v>
       </c>
       <c r="I68" s="5">
-        <f t="shared" ref="I68:AF68" si="9">I63</f>
-        <v>188.4504940011895</v>
+        <f t="shared" si="8"/>
+        <v>2579.6280722494112</v>
       </c>
       <c r="J68" s="5">
-        <f t="shared" si="9"/>
-        <v>182.96164466134903</v>
+        <f t="shared" si="8"/>
+        <v>2607.4715657030551</v>
       </c>
       <c r="K68" s="5">
-        <f t="shared" si="9"/>
-        <v>177.63266471975632</v>
+        <f t="shared" si="8"/>
+        <v>2637.5199855509622</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" si="9"/>
-        <v>172.45889778617118</v>
+        <f t="shared" si="8"/>
+        <v>2669.5709726607206</v>
       </c>
       <c r="M68" s="5">
-        <f t="shared" si="9"/>
-        <v>167.43582309337009</v>
+        <f t="shared" si="8"/>
+        <v>2692.8330628056278</v>
       </c>
       <c r="N68" s="5">
-        <f t="shared" si="9"/>
-        <v>162.55905154696123</v>
+        <f t="shared" si="8"/>
+        <v>2715.0603144269971</v>
       </c>
       <c r="O68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>157.82432189025366</v>
       </c>
       <c r="P68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>153.22749698082879</v>
       </c>
       <c r="Q68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>148.76456017556194</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF68" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>41</v>
       </c>
@@ -9166,123 +9167,123 @@
         <v>6868.4402011018146</v>
       </c>
       <c r="D69" s="5">
-        <f t="shared" ref="D69:G69" si="10">C6+D64</f>
+        <f t="shared" ref="D69:AF69" si="9">C6+D64</f>
         <v>3805.0788061456087</v>
       </c>
       <c r="E69" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3662.355308727233</v>
       </c>
       <c r="F69" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2999.2858045496764</v>
       </c>
       <c r="G69" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2492.4252043210045</v>
       </c>
       <c r="H69" s="5">
-        <f>H64</f>
-        <v>93.406361156067433</v>
+        <f t="shared" si="9"/>
+        <v>2355.6859555808901</v>
       </c>
       <c r="I69" s="5">
-        <f t="shared" ref="I69:AF69" si="11">I64</f>
-        <v>90.685787530162571</v>
+        <f t="shared" si="9"/>
+        <v>2224.0661798520518</v>
       </c>
       <c r="J69" s="5">
-        <f t="shared" si="11"/>
-        <v>88.04445391277919</v>
+        <f t="shared" si="9"/>
+        <v>2167.4924466149887</v>
       </c>
       <c r="K69" s="5">
-        <f t="shared" si="11"/>
-        <v>85.480052342504052</v>
+        <f t="shared" si="9"/>
+        <v>2112.6190346880921</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="11"/>
-        <v>82.990342080101016</v>
+        <f t="shared" si="9"/>
+        <v>2059.3856145068316</v>
       </c>
       <c r="M69" s="5">
-        <f t="shared" si="11"/>
-        <v>80.573147650583522</v>
+        <f t="shared" si="9"/>
+        <v>2006.7216198707158</v>
       </c>
       <c r="N69" s="5">
-        <f t="shared" si="11"/>
-        <v>78.226356942314084</v>
+        <f t="shared" si="9"/>
+        <v>1955.3640812230597</v>
       </c>
       <c r="O69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>75.947919361469985</v>
       </c>
       <c r="P69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>73.735844040262123</v>
       </c>
       <c r="Q69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>71.588198097341873</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF69" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.35">
       <c r="D73" s="22" t="s">
         <v>100</v>
       </c>
@@ -9293,7 +9294,7 @@
       <c r="I73" s="22"/>
       <c r="J73" s="22"/>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.35">
       <c r="D74" s="22" t="s">
         <v>101</v>
       </c>
@@ -9304,7 +9305,7 @@
       <c r="I74" s="22"/>
       <c r="J74" s="22"/>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.35">
       <c r="D75" s="22">
         <v>2020</v>
       </c>
@@ -9327,7 +9328,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.35">
       <c r="D76" s="40">
         <v>0.2467</v>
       </c>
@@ -9352,7 +9353,7 @@
         <v>0.46560000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B78" s="22"/>
       <c r="C78" s="22">
         <v>2012</v>
@@ -9427,7 +9428,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B79" s="22" t="s">
         <v>102</v>
       </c>
@@ -9505,7 +9506,7 @@
         <v>0.52875169540346068</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>103</v>
       </c>
@@ -9525,7 +9526,7 @@
       <c r="K82" s="17"/>
       <c r="L82" s="15"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>104</v>
       </c>
@@ -9548,7 +9549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>105</v>
       </c>
@@ -9571,7 +9572,7 @@
         <v>0.98556385942470071</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>106</v>
       </c>
@@ -9594,7 +9595,7 @@
         <v>0.96983137334414704</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>107</v>
       </c>
@@ -9617,7 +9618,7 @@
         <v>0.9686815713640794</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>108</v>
       </c>
@@ -9640,7 +9641,7 @@
         <v>0.95661376543184151</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>109</v>
       </c>
@@ -9663,7 +9664,7 @@
         <v>0.93665959530026111</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>110</v>
       </c>
@@ -9686,7 +9687,7 @@
         <v>0.9143273584567535</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>111</v>
       </c>
@@ -9709,7 +9710,7 @@
         <v>0.89805481563188172</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>112</v>
       </c>
@@ -9732,7 +9733,7 @@
         <v>0.88711067149387013</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>113</v>
       </c>
@@ -9755,7 +9756,7 @@
         <v>0.84730412960844359</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>114</v>
       </c>
@@ -9778,7 +9779,7 @@
         <v>0.78452102304761584</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>115</v>
       </c>
@@ -9795,7 +9796,7 @@
         <v>0.75350342301658668</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>116</v>
       </c>
@@ -9812,7 +9813,7 @@
         <v>0.73191600598044548</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>2025</v>
       </c>
@@ -9829,7 +9830,7 @@
         <v>0.71059806405868498</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>2026</v>
       </c>
@@ -9838,164 +9839,164 @@
         <v>332.79266010000003</v>
       </c>
       <c r="F98" s="16">
-        <f t="shared" ref="F98:F107" si="12">G$82</f>
+        <f t="shared" ref="F98:F107" si="10">G$82</f>
         <v>0.03</v>
       </c>
       <c r="G98" s="22">
-        <f t="shared" ref="G98:G107" si="13">D$84/D98</f>
+        <f t="shared" ref="G98:G107" si="11">D$84/D98</f>
         <v>0.68990103306668438</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>2027</v>
       </c>
       <c r="D99">
-        <f t="shared" ref="D99:D107" si="14">D98*(1+F99)</f>
+        <f t="shared" ref="D99:D107" si="12">D98*(1+F99)</f>
         <v>342.77643990300004</v>
       </c>
       <c r="F99" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G99" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.66980682822008197</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>2028</v>
       </c>
       <c r="D100">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>353.05973310009006</v>
       </c>
       <c r="F100" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G100" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.65029789147580774</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>2029</v>
       </c>
       <c r="D101">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>363.65152509309274</v>
       </c>
       <c r="F101" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G101" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.63135717619010456</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>2030</v>
       </c>
       <c r="D102">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>374.56107084588552</v>
       </c>
       <c r="F102" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G102" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.61296813222340252</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2031</v>
       </c>
       <c r="D103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>385.79790297126209</v>
       </c>
       <c r="F103" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G103" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.59511469147903162</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2032</v>
       </c>
       <c r="D104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>397.37184006039996</v>
       </c>
       <c r="F104" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G104" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.57778125386313739</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>2033</v>
       </c>
       <c r="D105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>409.29299526221195</v>
       </c>
       <c r="F105" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G105" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.56095267365353152</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>2034</v>
       </c>
       <c r="D106">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>421.57178512007829</v>
       </c>
       <c r="F106" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G106" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.54461424626556454</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>2035</v>
       </c>
       <c r="D107">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>434.21893867368067</v>
       </c>
       <c r="F107" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G107" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.52875169540346068</v>
       </c>
     </row>
@@ -10013,17 +10014,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4700B1-78D7-456C-A4C4-AB085247994E}">
   <dimension ref="A1:AL776"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.85546875" style="22" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="22" customWidth="1"/>
-    <col min="5" max="38" width="7.5703125" style="22" customWidth="1"/>
-    <col min="39" max="16384" width="12.5703125" style="22"/>
+    <col min="1" max="1" width="51.81640625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="22" customWidth="1"/>
+    <col min="5" max="38" width="7.54296875" style="22" customWidth="1"/>
+    <col min="39" max="16384" width="12.54296875" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>48</v>
       </c>
@@ -10065,7 +10066,7 @@
       <c r="AK1" s="21"/>
       <c r="AL1" s="21"/>
     </row>
-    <row r="2" spans="1:38" ht="102.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" ht="104.5" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
         <v>69</v>
       </c>
@@ -10107,7 +10108,7 @@
       <c r="AK2" s="24"/>
       <c r="AL2" s="24"/>
     </row>
-    <row r="3" spans="1:38" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -10147,7 +10148,7 @@
       <c r="AK3" s="24"/>
       <c r="AL3" s="24"/>
     </row>
-    <row r="4" spans="1:38" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
         <v>70</v>
       </c>
@@ -10191,7 +10192,7 @@
       <c r="AK4" s="24"/>
       <c r="AL4" s="24"/>
     </row>
-    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
         <v>71</v>
       </c>
@@ -10235,7 +10236,7 @@
       <c r="AK5" s="24"/>
       <c r="AL5" s="24"/>
     </row>
-    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -10275,7 +10276,7 @@
       <c r="AK6" s="24"/>
       <c r="AL6" s="24"/>
     </row>
-    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="22">
         <v>2023</v>
       </c>
@@ -10307,7 +10308,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>72</v>
       </c>
@@ -10320,11 +10321,11 @@
         <v>25177.910605727324</v>
       </c>
       <c r="D8" s="26">
-        <f>$B4*$B$16*E$14</f>
+        <f t="shared" si="0"/>
         <v>24444.573403618764</v>
       </c>
       <c r="E8" s="26">
-        <f>$B4*$B$16*F$14</f>
+        <f t="shared" si="0"/>
         <v>23732.595537493944</v>
       </c>
       <c r="F8" s="26">
@@ -10352,7 +10353,7 @@
         <v>19875.675132891927</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>73</v>
       </c>
@@ -10397,7 +10398,7 @@
         <v>23111.250154525496</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>122</v>
       </c>
@@ -10442,7 +10443,7 @@
         <v>7566.1942040579743</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
         <v>49</v>
       </c>
@@ -10484,7 +10485,7 @@
       <c r="AK12" s="21"/>
       <c r="AL12" s="21"/>
     </row>
-    <row r="13" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" ht="13" x14ac:dyDescent="0.3">
       <c r="B13" s="25">
         <v>2022</v>
       </c>
@@ -10519,7 +10520,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>121</v>
       </c>
@@ -10558,10 +10559,10 @@
         <v>0.57778125386313739</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
     </row>
-    <row r="16" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>50</v>
       </c>
@@ -10569,22 +10570,22 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="25"/>
     </row>
-    <row r="18" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:33" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:33" ht="39" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>53</v>
       </c>
@@ -10598,7 +10599,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="26" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
         <v>56</v>
       </c>
@@ -10613,7 +10614,7 @@
         <v>5883.907672857119</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="26" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>59</v>
       </c>
@@ -10628,7 +10629,7 @@
         <v>5883.907672857119</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="26" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>61</v>
       </c>
@@ -10643,13 +10644,13 @@
         <v>31380.840921904633</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
         <v>75</v>
       </c>
@@ -10686,7 +10687,7 @@
       <c r="AF28" s="29"/>
       <c r="AG28" s="29"/>
     </row>
-    <row r="29" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="30"/>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -10721,7 +10722,7 @@
       <c r="AF29" s="29"/>
       <c r="AG29" s="29"/>
     </row>
-    <row r="30" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
         <v>64</v>
       </c>
@@ -10758,7 +10759,7 @@
       <c r="AF30" s="29"/>
       <c r="AG30" s="29"/>
     </row>
-    <row r="31" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A31" s="29" t="s">
         <v>76</v>
       </c>
@@ -10816,7 +10817,7 @@
       <c r="AE31" s="29"/>
       <c r="AF31" s="29"/>
     </row>
-    <row r="32" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="13" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
         <v>65</v>
       </c>
@@ -10874,7 +10875,7 @@
       <c r="AE32" s="33"/>
       <c r="AF32" s="29"/>
     </row>
-    <row r="33" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="29" t="s">
         <v>66</v>
       </c>
@@ -10932,7 +10933,7 @@
       <c r="AE33" s="33"/>
       <c r="AF33" s="29"/>
     </row>
-    <row r="34" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" ht="13" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
         <v>67</v>
       </c>
@@ -10990,7 +10991,7 @@
       <c r="AE34" s="33"/>
       <c r="AF34" s="29"/>
     </row>
-    <row r="36" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>68</v>
       </c>
@@ -11057,746 +11058,746 @@
       <c r="AC36" s="26"/>
       <c r="AD36" s="26"/>
     </row>
-    <row r="37" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="13" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11809,7 +11810,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11821,13 +11822,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="53.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="2" max="2" width="53.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -11922,7 +11923,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11948,31 +11949,31 @@
       </c>
       <c r="G2" s="18">
         <f>'Passenger Vehicle Calculations'!H68</f>
-        <v>194.10400882122519</v>
+        <v>3312.3286898445285</v>
       </c>
       <c r="H2" s="18">
         <f>'Passenger Vehicle Calculations'!I68</f>
-        <v>188.4504940011895</v>
+        <v>2579.6280722494112</v>
       </c>
       <c r="I2" s="18">
         <f>'Passenger Vehicle Calculations'!J68</f>
-        <v>182.96164466134903</v>
+        <v>2607.4715657030551</v>
       </c>
       <c r="J2" s="18">
         <f>'Passenger Vehicle Calculations'!K68</f>
-        <v>177.63266471975632</v>
+        <v>2637.5199855509622</v>
       </c>
       <c r="K2" s="18">
         <f>'Passenger Vehicle Calculations'!L68</f>
-        <v>172.45889778617118</v>
+        <v>2669.5709726607206</v>
       </c>
       <c r="L2" s="18">
         <f>'Passenger Vehicle Calculations'!M68</f>
-        <v>167.43582309337009</v>
+        <v>2692.8330628056278</v>
       </c>
       <c r="M2" s="18">
         <f>'Passenger Vehicle Calculations'!N68</f>
-        <v>162.55905154696123</v>
+        <v>2715.0603144269971</v>
       </c>
       <c r="N2" s="18">
         <f>'Passenger Vehicle Calculations'!O68</f>
@@ -12047,7 +12048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12142,7 +12143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12237,7 +12238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12332,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12358,31 +12359,31 @@
       </c>
       <c r="G6" s="18">
         <f>'Passenger Vehicle Calculations'!H69</f>
-        <v>93.406361156067433</v>
+        <v>2355.6859555808901</v>
       </c>
       <c r="H6" s="18">
         <f>'Passenger Vehicle Calculations'!I69</f>
-        <v>90.685787530162571</v>
+        <v>2224.0661798520518</v>
       </c>
       <c r="I6" s="18">
         <f>'Passenger Vehicle Calculations'!J69</f>
-        <v>88.04445391277919</v>
+        <v>2167.4924466149887</v>
       </c>
       <c r="J6" s="18">
         <f>'Passenger Vehicle Calculations'!K69</f>
-        <v>85.480052342504052</v>
+        <v>2112.6190346880921</v>
       </c>
       <c r="K6" s="18">
         <f>'Passenger Vehicle Calculations'!L69</f>
-        <v>82.990342080101016</v>
+        <v>2059.3856145068316</v>
       </c>
       <c r="L6" s="18">
         <f>'Passenger Vehicle Calculations'!M69</f>
-        <v>80.573147650583522</v>
+        <v>2006.7216198707158</v>
       </c>
       <c r="M6" s="18">
         <f>'Passenger Vehicle Calculations'!N69</f>
-        <v>78.226356942314084</v>
+        <v>1955.3640812230597</v>
       </c>
       <c r="N6" s="18">
         <f>'Passenger Vehicle Calculations'!O69</f>
@@ -12457,7 +12458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -12552,7 +12553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -12576,31 +12577,31 @@
       </c>
       <c r="G8" s="18">
         <f t="shared" si="0"/>
-        <v>194.10400882122519</v>
+        <v>3312.3286898445285</v>
       </c>
       <c r="H8" s="18">
         <f t="shared" si="0"/>
-        <v>188.4504940011895</v>
+        <v>2579.6280722494112</v>
       </c>
       <c r="I8" s="18">
         <f t="shared" si="0"/>
-        <v>182.96164466134903</v>
+        <v>2607.4715657030551</v>
       </c>
       <c r="J8" s="18">
         <f t="shared" si="0"/>
-        <v>177.63266471975632</v>
+        <v>2637.5199855509622</v>
       </c>
       <c r="K8" s="18">
         <f t="shared" si="0"/>
-        <v>172.45889778617118</v>
+        <v>2669.5709726607206</v>
       </c>
       <c r="L8" s="18">
         <f t="shared" si="0"/>
-        <v>167.43582309337009</v>
+        <v>2692.8330628056278</v>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>162.55905154696123</v>
+        <v>2715.0603144269971</v>
       </c>
       <c r="N8" s="18">
         <f t="shared" si="0"/>
@@ -12687,13 +12688,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -12788,7 +12789,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12811,82 +12812,89 @@
         <v>24444.57340361876</v>
       </c>
       <c r="G2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14*'Commercial Vehicles'!$B16</f>
+        <v>23732.59553749394</v>
       </c>
       <c r="H2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14*'Commercial Vehicles'!$B16</f>
+        <v>23041.354890770817</v>
       </c>
       <c r="I2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14*'Commercial Vehicles'!$B16</f>
+        <v>22370.247466767789</v>
       </c>
       <c r="J2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14*'Commercial Vehicles'!$B16</f>
+        <v>21718.686860939597</v>
       </c>
       <c r="K2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14*'Commercial Vehicles'!$B16</f>
+        <v>21086.103748485046</v>
       </c>
       <c r="L2" s="51">
-        <v>0</v>
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14*'Commercial Vehicles'!$B16</f>
+        <v>20471.945386878688</v>
       </c>
       <c r="M2" s="51">
-        <v>0</v>
-      </c>
-      <c r="N2" s="51">
-        <v>0</v>
-      </c>
-      <c r="O2" s="51">
-        <v>0</v>
-      </c>
-      <c r="P2" s="51">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="51">
-        <v>0</v>
-      </c>
-      <c r="R2" s="51">
-        <v>0</v>
-      </c>
-      <c r="S2" s="51">
-        <v>0</v>
-      </c>
-      <c r="T2" s="51">
-        <v>0</v>
-      </c>
-      <c r="U2" s="51">
-        <v>0</v>
-      </c>
-      <c r="V2" s="51">
-        <v>0</v>
-      </c>
-      <c r="W2" s="51">
-        <v>0</v>
-      </c>
-      <c r="X2" s="51">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="51">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="51">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14*'Commercial Vehicles'!$B16</f>
+        <v>19875.675132891927</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12981,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13076,7 +13084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13171,7 +13179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13195,31 +13203,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23732.59553749394</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23041.354890770817</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22370.247466767789</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21718.686860939597</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21086.103748485046</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20471.945386878688</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19875.675132891927</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -13276,7 +13284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -13371,7 +13379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -13395,31 +13403,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23732.59553749394</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23041.354890770817</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22370.247466767789</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21718.686860939597</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21086.103748485046</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20471.945386878688</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19875.675132891927</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -13487,12 +13495,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -13587,7 +13595,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13682,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13777,7 +13785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13872,7 +13880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13967,7 +13975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14062,7 +14070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -14157,7 +14165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -14263,12 +14271,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -14363,7 +14371,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14458,7 +14466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14553,7 +14561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14648,7 +14656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14743,7 +14751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14838,7 +14846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -14933,7 +14941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -15039,12 +15047,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -15139,7 +15147,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15234,7 +15242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15329,7 +15337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -15424,7 +15432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15519,7 +15527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15614,7 +15622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -15709,7 +15717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>

--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\trans\BVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEC4C98-09EB-4A72-B928-46EF777001B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72764887-92EB-4105-8C57-DAC59B97E0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8835" yWindow="360" windowWidth="20295" windowHeight="12150" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="BVS-psgr-LDVs" sheetId="2" r:id="rId5"/>
     <sheet name="BVS-psgr-HDVs" sheetId="101" r:id="rId6"/>
     <sheet name="BVS-psgr-aircraft" sheetId="105" r:id="rId7"/>
-    <sheet name="BVP-psgr-rail" sheetId="104" r:id="rId8"/>
+    <sheet name="BVS-psgr-rail" sheetId="104" r:id="rId8"/>
     <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId9"/>
     <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId10"/>
     <sheet name="frgt" sheetId="106" r:id="rId11"/>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="124">
   <si>
     <t>Sources:</t>
   </si>
@@ -515,6 +515,9 @@
   <si>
     <t>Frgt LDV (2012 $)</t>
   </si>
+  <si>
+    <t>took out IRA</t>
+  </si>
 </sst>
 </file>
 
@@ -668,7 +671,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,6 +705,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,7 +836,7 @@
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -900,6 +909,7 @@
     <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="34">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1304,17 +1314,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="69.26953125" customWidth="1"/>
+    <col min="2" max="2" width="69.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,47 +1332,47 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
     </row>
   </sheetData>
@@ -1378,12 +1388,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1478,7 +1488,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1573,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1668,7 +1678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1763,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1858,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1953,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2048,7 +2058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2154,7 +2164,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2166,12 +2176,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -2266,7 +2276,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2289,32 +2299,25 @@
         <v>9098.157067904207</v>
       </c>
       <c r="G2">
-        <f>'Commercial Vehicles'!E10</f>
-        <v>8900.5394373583313</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <f>'Commercial Vehicles'!F10</f>
-        <v>8762.1955571514172</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <f>'Commercial Vehicles'!G10</f>
-        <v>8574.638599520662</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <f>'Commercial Vehicles'!H10</f>
-        <v>8327.2183891071436</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <f>'Commercial Vehicles'!I10</f>
-        <v>8038.2687173078502</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <f>'Commercial Vehicles'!J10</f>
-        <v>7772.0490463949827</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <f>'Commercial Vehicles'!K10</f>
-        <v>7566.1942040579743</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -2371,7 +2374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2561,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2680,31 +2683,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>8900.5394373583313</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>8762.1955571514172</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>8574.638599520662</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>8327.2183891071436</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>8038.2687173078502</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>7772.0490463949827</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>7566.1942040579743</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2761,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2856,7 +2859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2880,31 +2883,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>8900.5394373583313</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>8762.1955571514172</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>8574.638599520662</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>8327.2183891071436</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>8038.2687173078502</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>7772.0490463949827</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>7566.1942040579743</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2973,13 +2976,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3074,7 +3077,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3097,89 +3100,82 @@
         <v>28423.922562347398</v>
       </c>
       <c r="G2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14</f>
-        <v>27596.041322667374</v>
+        <v>0</v>
       </c>
       <c r="H2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14</f>
-        <v>26792.273128803277</v>
+        <v>0</v>
       </c>
       <c r="I2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14</f>
-        <v>26011.915659032311</v>
+        <v>0</v>
       </c>
       <c r="J2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14</f>
-        <v>25254.287047604183</v>
+        <v>0</v>
       </c>
       <c r="K2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14</f>
-        <v>24518.725288936101</v>
+        <v>0</v>
       </c>
       <c r="L2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14</f>
-        <v>23804.587659161265</v>
+        <v>0</v>
       </c>
       <c r="M2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14</f>
-        <v>23111.250154525496</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="N2" s="51">
+        <v>0</v>
+      </c>
+      <c r="O2" s="51">
+        <v>0</v>
+      </c>
+      <c r="P2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="51">
+        <v>0</v>
+      </c>
+      <c r="R2" s="51">
+        <v>0</v>
+      </c>
+      <c r="S2" s="51">
+        <v>0</v>
+      </c>
+      <c r="T2" s="51">
+        <v>0</v>
+      </c>
+      <c r="U2" s="51">
+        <v>0</v>
+      </c>
+      <c r="V2" s="51">
+        <v>0</v>
+      </c>
+      <c r="W2" s="51">
+        <v>0</v>
+      </c>
+      <c r="X2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3274,7 +3270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3369,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3464,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3488,31 +3484,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>27596.041322667374</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>26792.273128803277</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>26011.915659032311</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>25254.287047604183</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>24518.725288936101</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>23804.587659161265</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>23111.250154525496</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3569,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3664,7 +3660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3688,31 +3684,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>27596.041322667374</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>26792.273128803277</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>26011.915659032311</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>25254.287047604183</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>24518.725288936101</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>23804.587659161265</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>23111.250154525496</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3780,12 +3776,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3880,7 +3876,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3975,7 +3971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4070,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4165,7 +4161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4260,7 +4256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4355,7 +4351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4450,7 +4446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4556,12 +4552,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -4656,7 +4652,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4751,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4846,7 +4842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4941,7 +4937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5036,7 +5032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5131,7 +5127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5226,7 +5222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5332,12 +5328,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5432,7 +5428,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5527,7 +5523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5622,7 +5618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5717,7 +5713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5812,7 +5808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5907,7 +5903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6002,7 +5998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6108,12 +6104,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -6208,7 +6204,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6303,7 +6299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6398,7 +6394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6493,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6588,7 +6584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6683,7 +6679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6778,7 +6774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6881,34 +6877,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8A3CC6-8591-4A07-9E4B-1DE39D29E87F}">
   <dimension ref="A1:AF107"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.453125" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
-    <col min="4" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2021</v>
       </c>
@@ -7000,7 +6996,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
@@ -7095,7 +7091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
@@ -7190,34 +7186,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>119</v>
       </c>
       <c r="B12" s="7"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>13</v>
       </c>
@@ -7226,7 +7222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>15</v>
       </c>
@@ -7235,13 +7231,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="8"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>18</v>
       </c>
@@ -7285,7 +7281,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
         <v>21</v>
       </c>
@@ -7325,7 +7321,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
         <v>23</v>
       </c>
@@ -7373,7 +7369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
@@ -7415,7 +7411,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>26</v>
       </c>
@@ -7461,7 +7457,7 @@
       </c>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>27</v>
       </c>
@@ -7498,7 +7494,7 @@
       <c r="L21" s="10"/>
       <c r="M21" s="11"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>29</v>
       </c>
@@ -7541,7 +7537,7 @@
       </c>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>30</v>
       </c>
@@ -7578,7 +7574,7 @@
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
     </row>
-    <row r="24" spans="1:18" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>31</v>
       </c>
@@ -7614,7 +7610,7 @@
       </c>
       <c r="R24" s="12"/>
     </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>90</v>
       </c>
@@ -7649,7 +7645,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
@@ -7681,7 +7677,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
@@ -7713,7 +7709,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>92</v>
       </c>
@@ -7749,7 +7745,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>94</v>
       </c>
@@ -7781,7 +7777,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>34</v>
       </c>
@@ -7816,7 +7812,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
@@ -7861,7 +7857,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>36</v>
       </c>
@@ -7896,7 +7892,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>37</v>
       </c>
@@ -7928,7 +7924,7 @@
       </c>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>38</v>
       </c>
@@ -7936,11 +7932,11 @@
         <v>329.5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
     </row>
-    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>99</v>
       </c>
@@ -7978,7 +7974,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
         <v>21</v>
       </c>
@@ -8018,7 +8014,7 @@
       </c>
       <c r="L37"/>
     </row>
-    <row r="38" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
         <v>23</v>
       </c>
@@ -8058,7 +8054,7 @@
       </c>
       <c r="L38"/>
     </row>
-    <row r="39" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>25</v>
       </c>
@@ -8092,7 +8088,7 @@
       </c>
       <c r="L39"/>
     </row>
-    <row r="40" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>26</v>
       </c>
@@ -8132,7 +8128,7 @@
       </c>
       <c r="L40"/>
     </row>
-    <row r="41" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>27</v>
       </c>
@@ -8165,7 +8161,7 @@
       </c>
       <c r="L41"/>
     </row>
-    <row r="42" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>29</v>
       </c>
@@ -8202,7 +8198,7 @@
       </c>
       <c r="L42"/>
     </row>
-    <row r="43" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>30</v>
       </c>
@@ -8235,7 +8231,7 @@
       </c>
       <c r="L43"/>
     </row>
-    <row r="44" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>31</v>
       </c>
@@ -8268,7 +8264,7 @@
       </c>
       <c r="L44"/>
     </row>
-    <row r="45" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>90</v>
       </c>
@@ -8301,7 +8297,7 @@
       </c>
       <c r="L45"/>
     </row>
-    <row r="46" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>32</v>
       </c>
@@ -8334,7 +8330,7 @@
       </c>
       <c r="L46"/>
     </row>
-    <row r="47" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>33</v>
       </c>
@@ -8368,7 +8364,7 @@
       </c>
       <c r="L47"/>
     </row>
-    <row r="48" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>92</v>
       </c>
@@ -8402,7 +8398,7 @@
       </c>
       <c r="L48"/>
     </row>
-    <row r="49" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>94</v>
       </c>
@@ -8435,7 +8431,7 @@
       </c>
       <c r="L49"/>
     </row>
-    <row r="50" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>34</v>
       </c>
@@ -8468,7 +8464,7 @@
       </c>
       <c r="L50"/>
     </row>
-    <row r="51" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>35</v>
       </c>
@@ -8508,7 +8504,7 @@
       </c>
       <c r="L51"/>
     </row>
-    <row r="52" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>36</v>
       </c>
@@ -8541,7 +8537,7 @@
       </c>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>37</v>
       </c>
@@ -8573,7 +8569,7 @@
       </c>
       <c r="L53"/>
     </row>
-    <row r="54" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>38</v>
       </c>
@@ -8582,11 +8578,11 @@
       </c>
       <c r="L54"/>
     </row>
-    <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
     </row>
-    <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -8598,13 +8594,13 @@
       <c r="I56" s="8"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>44</v>
       </c>
@@ -8612,15 +8608,15 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C62">
         <v>2021</v>
       </c>
@@ -8712,7 +8708,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>40</v>
       </c>
@@ -8822,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>41</v>
       </c>
@@ -8932,15 +8928,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="H66" s="52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C67">
         <v>2021</v>
       </c>
@@ -9032,17 +9031,17 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5">
-        <f t="shared" ref="C68:AF68" si="8">B5+C63</f>
+        <f>B5+C63</f>
         <v>1930.7404811231229</v>
       </c>
       <c r="D68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="D68:G68" si="8">C5+D63</f>
         <v>1599.8025784220101</v>
       </c>
       <c r="E68" s="5">
@@ -9050,7 +9049,7 @@
         <v>5130.1015918271351</v>
       </c>
       <c r="F68" s="5">
-        <f t="shared" si="8"/>
+        <f>E5+F63</f>
         <v>3819.9265877142789</v>
       </c>
       <c r="G68" s="5">
@@ -9058,107 +9057,107 @@
         <v>3565.6148024975096</v>
       </c>
       <c r="H68" s="5">
-        <f t="shared" si="8"/>
-        <v>3312.3286898445285</v>
+        <f>H63</f>
+        <v>194.10400882122519</v>
       </c>
       <c r="I68" s="5">
-        <f t="shared" si="8"/>
-        <v>2579.6280722494112</v>
+        <f t="shared" ref="I68:AF68" si="9">I63</f>
+        <v>188.4504940011895</v>
       </c>
       <c r="J68" s="5">
-        <f t="shared" si="8"/>
-        <v>2607.4715657030551</v>
+        <f t="shared" si="9"/>
+        <v>182.96164466134903</v>
       </c>
       <c r="K68" s="5">
-        <f t="shared" si="8"/>
-        <v>2637.5199855509622</v>
+        <f t="shared" si="9"/>
+        <v>177.63266471975632</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" si="8"/>
-        <v>2669.5709726607206</v>
+        <f t="shared" si="9"/>
+        <v>172.45889778617118</v>
       </c>
       <c r="M68" s="5">
-        <f t="shared" si="8"/>
-        <v>2692.8330628056278</v>
+        <f t="shared" si="9"/>
+        <v>167.43582309337009</v>
       </c>
       <c r="N68" s="5">
-        <f t="shared" si="8"/>
-        <v>2715.0603144269971</v>
+        <f t="shared" si="9"/>
+        <v>162.55905154696123</v>
       </c>
       <c r="O68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>157.82432189025366</v>
       </c>
       <c r="P68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>153.22749698082879</v>
       </c>
       <c r="Q68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>148.76456017556194</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF68" s="5">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>41</v>
       </c>
@@ -9167,123 +9166,123 @@
         <v>6868.4402011018146</v>
       </c>
       <c r="D69" s="5">
-        <f t="shared" ref="D69:AF69" si="9">C6+D64</f>
+        <f t="shared" ref="D69:G69" si="10">C6+D64</f>
         <v>3805.0788061456087</v>
       </c>
       <c r="E69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3662.355308727233</v>
       </c>
       <c r="F69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2999.2858045496764</v>
       </c>
       <c r="G69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2492.4252043210045</v>
       </c>
       <c r="H69" s="5">
-        <f t="shared" si="9"/>
-        <v>2355.6859555808901</v>
+        <f>H64</f>
+        <v>93.406361156067433</v>
       </c>
       <c r="I69" s="5">
-        <f t="shared" si="9"/>
-        <v>2224.0661798520518</v>
+        <f t="shared" ref="I69:AF69" si="11">I64</f>
+        <v>90.685787530162571</v>
       </c>
       <c r="J69" s="5">
-        <f t="shared" si="9"/>
-        <v>2167.4924466149887</v>
+        <f t="shared" si="11"/>
+        <v>88.04445391277919</v>
       </c>
       <c r="K69" s="5">
-        <f t="shared" si="9"/>
-        <v>2112.6190346880921</v>
+        <f t="shared" si="11"/>
+        <v>85.480052342504052</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="9"/>
-        <v>2059.3856145068316</v>
+        <f t="shared" si="11"/>
+        <v>82.990342080101016</v>
       </c>
       <c r="M69" s="5">
-        <f t="shared" si="9"/>
-        <v>2006.7216198707158</v>
+        <f t="shared" si="11"/>
+        <v>80.573147650583522</v>
       </c>
       <c r="N69" s="5">
-        <f t="shared" si="9"/>
-        <v>1955.3640812230597</v>
+        <f t="shared" si="11"/>
+        <v>78.226356942314084</v>
       </c>
       <c r="O69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>75.947919361469985</v>
       </c>
       <c r="P69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>73.735844040262123</v>
       </c>
       <c r="Q69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>71.588198097341873</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="W69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="X69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Y69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Z69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AB69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AD69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AF69" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="D73" s="22" t="s">
         <v>100</v>
       </c>
@@ -9294,7 +9293,7 @@
       <c r="I73" s="22"/>
       <c r="J73" s="22"/>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="D74" s="22" t="s">
         <v>101</v>
       </c>
@@ -9305,7 +9304,7 @@
       <c r="I74" s="22"/>
       <c r="J74" s="22"/>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="D75" s="22">
         <v>2020</v>
       </c>
@@ -9328,7 +9327,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="D76" s="40">
         <v>0.2467</v>
       </c>
@@ -9353,7 +9352,7 @@
         <v>0.46560000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B78" s="22"/>
       <c r="C78" s="22">
         <v>2012</v>
@@ -9428,7 +9427,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B79" s="22" t="s">
         <v>102</v>
       </c>
@@ -9506,7 +9505,7 @@
         <v>0.52875169540346068</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>103</v>
       </c>
@@ -9526,7 +9525,7 @@
       <c r="K82" s="17"/>
       <c r="L82" s="15"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>104</v>
       </c>
@@ -9549,7 +9548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>105</v>
       </c>
@@ -9572,7 +9571,7 @@
         <v>0.98556385942470071</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>106</v>
       </c>
@@ -9595,7 +9594,7 @@
         <v>0.96983137334414704</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>107</v>
       </c>
@@ -9618,7 +9617,7 @@
         <v>0.9686815713640794</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>108</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>0.95661376543184151</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>109</v>
       </c>
@@ -9664,7 +9663,7 @@
         <v>0.93665959530026111</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>110</v>
       </c>
@@ -9687,7 +9686,7 @@
         <v>0.9143273584567535</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>111</v>
       </c>
@@ -9710,7 +9709,7 @@
         <v>0.89805481563188172</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>112</v>
       </c>
@@ -9733,7 +9732,7 @@
         <v>0.88711067149387013</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>113</v>
       </c>
@@ -9756,7 +9755,7 @@
         <v>0.84730412960844359</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>114</v>
       </c>
@@ -9779,7 +9778,7 @@
         <v>0.78452102304761584</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>115</v>
       </c>
@@ -9796,7 +9795,7 @@
         <v>0.75350342301658668</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>116</v>
       </c>
@@ -9813,7 +9812,7 @@
         <v>0.73191600598044548</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2025</v>
       </c>
@@ -9830,7 +9829,7 @@
         <v>0.71059806405868498</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2026</v>
       </c>
@@ -9839,164 +9838,164 @@
         <v>332.79266010000003</v>
       </c>
       <c r="F98" s="16">
-        <f t="shared" ref="F98:F107" si="10">G$82</f>
+        <f t="shared" ref="F98:F107" si="12">G$82</f>
         <v>0.03</v>
       </c>
       <c r="G98" s="22">
-        <f t="shared" ref="G98:G107" si="11">D$84/D98</f>
+        <f t="shared" ref="G98:G107" si="13">D$84/D98</f>
         <v>0.68990103306668438</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2027</v>
       </c>
       <c r="D99">
-        <f t="shared" ref="D99:D107" si="12">D98*(1+F99)</f>
+        <f t="shared" ref="D99:D107" si="14">D98*(1+F99)</f>
         <v>342.77643990300004</v>
       </c>
       <c r="F99" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.03</v>
       </c>
       <c r="G99" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.66980682822008197</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2028</v>
       </c>
       <c r="D100">
+        <f t="shared" si="14"/>
+        <v>353.05973310009006</v>
+      </c>
+      <c r="F100" s="16">
         <f t="shared" si="12"/>
-        <v>353.05973310009006</v>
-      </c>
-      <c r="F100" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G100" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.65029789147580774</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2029</v>
       </c>
       <c r="D101">
+        <f t="shared" si="14"/>
+        <v>363.65152509309274</v>
+      </c>
+      <c r="F101" s="16">
         <f t="shared" si="12"/>
-        <v>363.65152509309274</v>
-      </c>
-      <c r="F101" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G101" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.63135717619010456</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2030</v>
       </c>
       <c r="D102">
+        <f t="shared" si="14"/>
+        <v>374.56107084588552</v>
+      </c>
+      <c r="F102" s="16">
         <f t="shared" si="12"/>
-        <v>374.56107084588552</v>
-      </c>
-      <c r="F102" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G102" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.61296813222340252</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2031</v>
       </c>
       <c r="D103">
+        <f t="shared" si="14"/>
+        <v>385.79790297126209</v>
+      </c>
+      <c r="F103" s="16">
         <f t="shared" si="12"/>
-        <v>385.79790297126209</v>
-      </c>
-      <c r="F103" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G103" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.59511469147903162</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2032</v>
       </c>
       <c r="D104">
+        <f t="shared" si="14"/>
+        <v>397.37184006039996</v>
+      </c>
+      <c r="F104" s="16">
         <f t="shared" si="12"/>
-        <v>397.37184006039996</v>
-      </c>
-      <c r="F104" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G104" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.57778125386313739</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2033</v>
       </c>
       <c r="D105">
+        <f t="shared" si="14"/>
+        <v>409.29299526221195</v>
+      </c>
+      <c r="F105" s="16">
         <f t="shared" si="12"/>
-        <v>409.29299526221195</v>
-      </c>
-      <c r="F105" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G105" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.56095267365353152</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2034</v>
       </c>
       <c r="D106">
+        <f t="shared" si="14"/>
+        <v>421.57178512007829</v>
+      </c>
+      <c r="F106" s="16">
         <f t="shared" si="12"/>
-        <v>421.57178512007829</v>
-      </c>
-      <c r="F106" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G106" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.54461424626556454</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2035</v>
       </c>
       <c r="D107">
+        <f t="shared" si="14"/>
+        <v>434.21893867368067</v>
+      </c>
+      <c r="F107" s="16">
         <f t="shared" si="12"/>
-        <v>434.21893867368067</v>
-      </c>
-      <c r="F107" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G107" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.52875169540346068</v>
       </c>
     </row>
@@ -10014,17 +10013,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4700B1-78D7-456C-A4C4-AB085247994E}">
   <dimension ref="A1:AL776"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" style="22" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" style="22" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="22" customWidth="1"/>
-    <col min="5" max="38" width="7.54296875" style="22" customWidth="1"/>
-    <col min="39" max="16384" width="12.54296875" style="22"/>
+    <col min="1" max="1" width="51.85546875" style="22" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="22" customWidth="1"/>
+    <col min="5" max="38" width="7.5703125" style="22" customWidth="1"/>
+    <col min="39" max="16384" width="12.5703125" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>48</v>
       </c>
@@ -10066,7 +10065,7 @@
       <c r="AK1" s="21"/>
       <c r="AL1" s="21"/>
     </row>
-    <row r="2" spans="1:38" ht="104.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" ht="102.75" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>69</v>
       </c>
@@ -10108,7 +10107,7 @@
       <c r="AK2" s="24"/>
       <c r="AL2" s="24"/>
     </row>
-    <row r="3" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -10148,7 +10147,7 @@
       <c r="AK3" s="24"/>
       <c r="AL3" s="24"/>
     </row>
-    <row r="4" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:38" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>70</v>
       </c>
@@ -10192,7 +10191,7 @@
       <c r="AK4" s="24"/>
       <c r="AL4" s="24"/>
     </row>
-    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>71</v>
       </c>
@@ -10236,7 +10235,7 @@
       <c r="AK5" s="24"/>
       <c r="AL5" s="24"/>
     </row>
-    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -10276,7 +10275,7 @@
       <c r="AK6" s="24"/>
       <c r="AL6" s="24"/>
     </row>
-    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="22">
         <v>2023</v>
       </c>
@@ -10308,7 +10307,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
         <v>72</v>
       </c>
@@ -10321,11 +10320,11 @@
         <v>25177.910605727324</v>
       </c>
       <c r="D8" s="26">
-        <f t="shared" si="0"/>
+        <f>$B4*$B$16*E$14</f>
         <v>24444.573403618764</v>
       </c>
       <c r="E8" s="26">
-        <f t="shared" si="0"/>
+        <f>$B4*$B$16*F$14</f>
         <v>23732.595537493944</v>
       </c>
       <c r="F8" s="26">
@@ -10353,7 +10352,7 @@
         <v>19875.675132891927</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
         <v>73</v>
       </c>
@@ -10398,7 +10397,7 @@
         <v>23111.250154525496</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
         <v>122</v>
       </c>
@@ -10443,7 +10442,7 @@
         <v>7566.1942040579743</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>49</v>
       </c>
@@ -10485,7 +10484,7 @@
       <c r="AK12" s="21"/>
       <c r="AL12" s="21"/>
     </row>
-    <row r="13" spans="1:38" ht="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B13" s="25">
         <v>2022</v>
       </c>
@@ -10520,7 +10519,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="22" t="s">
         <v>121</v>
       </c>
@@ -10559,10 +10558,10 @@
         <v>0.57778125386313739</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
     </row>
-    <row r="16" spans="1:38" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
         <v>50</v>
       </c>
@@ -10570,22 +10569,22 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="25"/>
     </row>
-    <row r="18" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:33" ht="39" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:33" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
         <v>53</v>
       </c>
@@ -10599,7 +10598,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="26" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="s">
         <v>56</v>
       </c>
@@ -10614,7 +10613,7 @@
         <v>5883.907672857119</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A24" s="25" t="s">
         <v>59</v>
       </c>
@@ -10629,7 +10628,7 @@
         <v>5883.907672857119</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="26" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
         <v>61</v>
       </c>
@@ -10644,13 +10643,13 @@
         <v>31380.840921904633</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="29" t="s">
         <v>75</v>
       </c>
@@ -10687,7 +10686,7 @@
       <c r="AF28" s="29"/>
       <c r="AG28" s="29"/>
     </row>
-    <row r="29" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="30"/>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -10722,7 +10721,7 @@
       <c r="AF29" s="29"/>
       <c r="AG29" s="29"/>
     </row>
-    <row r="30" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="30" t="s">
         <v>64</v>
       </c>
@@ -10759,7 +10758,7 @@
       <c r="AF30" s="29"/>
       <c r="AG30" s="29"/>
     </row>
-    <row r="31" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="29" t="s">
         <v>76</v>
       </c>
@@ -10817,7 +10816,7 @@
       <c r="AE31" s="29"/>
       <c r="AF31" s="29"/>
     </row>
-    <row r="32" spans="1:33" ht="13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="29" t="s">
         <v>65</v>
       </c>
@@ -10875,7 +10874,7 @@
       <c r="AE32" s="33"/>
       <c r="AF32" s="29"/>
     </row>
-    <row r="33" spans="1:32" ht="13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="29" t="s">
         <v>66</v>
       </c>
@@ -10933,7 +10932,7 @@
       <c r="AE33" s="33"/>
       <c r="AF33" s="29"/>
     </row>
-    <row r="34" spans="1:32" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="29" t="s">
         <v>67</v>
       </c>
@@ -10991,7 +10990,7 @@
       <c r="AE34" s="33"/>
       <c r="AF34" s="29"/>
     </row>
-    <row r="36" spans="1:32" ht="13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>68</v>
       </c>
@@ -11058,746 +11057,746 @@
       <c r="AC36" s="26"/>
       <c r="AD36" s="26"/>
     </row>
-    <row r="37" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="13" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="13" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11810,7 +11809,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11822,13 +11821,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
-    <col min="2" max="2" width="53.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="53.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -11923,7 +11922,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11949,31 +11948,31 @@
       </c>
       <c r="G2" s="18">
         <f>'Passenger Vehicle Calculations'!H68</f>
-        <v>3312.3286898445285</v>
+        <v>194.10400882122519</v>
       </c>
       <c r="H2" s="18">
         <f>'Passenger Vehicle Calculations'!I68</f>
-        <v>2579.6280722494112</v>
+        <v>188.4504940011895</v>
       </c>
       <c r="I2" s="18">
         <f>'Passenger Vehicle Calculations'!J68</f>
-        <v>2607.4715657030551</v>
+        <v>182.96164466134903</v>
       </c>
       <c r="J2" s="18">
         <f>'Passenger Vehicle Calculations'!K68</f>
-        <v>2637.5199855509622</v>
+        <v>177.63266471975632</v>
       </c>
       <c r="K2" s="18">
         <f>'Passenger Vehicle Calculations'!L68</f>
-        <v>2669.5709726607206</v>
+        <v>172.45889778617118</v>
       </c>
       <c r="L2" s="18">
         <f>'Passenger Vehicle Calculations'!M68</f>
-        <v>2692.8330628056278</v>
+        <v>167.43582309337009</v>
       </c>
       <c r="M2" s="18">
         <f>'Passenger Vehicle Calculations'!N68</f>
-        <v>2715.0603144269971</v>
+        <v>162.55905154696123</v>
       </c>
       <c r="N2" s="18">
         <f>'Passenger Vehicle Calculations'!O68</f>
@@ -12048,7 +12047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12143,7 +12142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12238,7 +12237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12333,7 +12332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12359,31 +12358,31 @@
       </c>
       <c r="G6" s="18">
         <f>'Passenger Vehicle Calculations'!H69</f>
-        <v>2355.6859555808901</v>
+        <v>93.406361156067433</v>
       </c>
       <c r="H6" s="18">
         <f>'Passenger Vehicle Calculations'!I69</f>
-        <v>2224.0661798520518</v>
+        <v>90.685787530162571</v>
       </c>
       <c r="I6" s="18">
         <f>'Passenger Vehicle Calculations'!J69</f>
-        <v>2167.4924466149887</v>
+        <v>88.04445391277919</v>
       </c>
       <c r="J6" s="18">
         <f>'Passenger Vehicle Calculations'!K69</f>
-        <v>2112.6190346880921</v>
+        <v>85.480052342504052</v>
       </c>
       <c r="K6" s="18">
         <f>'Passenger Vehicle Calculations'!L69</f>
-        <v>2059.3856145068316</v>
+        <v>82.990342080101016</v>
       </c>
       <c r="L6" s="18">
         <f>'Passenger Vehicle Calculations'!M69</f>
-        <v>2006.7216198707158</v>
+        <v>80.573147650583522</v>
       </c>
       <c r="M6" s="18">
         <f>'Passenger Vehicle Calculations'!N69</f>
-        <v>1955.3640812230597</v>
+        <v>78.226356942314084</v>
       </c>
       <c r="N6" s="18">
         <f>'Passenger Vehicle Calculations'!O69</f>
@@ -12458,7 +12457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -12553,7 +12552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -12577,31 +12576,31 @@
       </c>
       <c r="G8" s="18">
         <f t="shared" si="0"/>
-        <v>3312.3286898445285</v>
+        <v>194.10400882122519</v>
       </c>
       <c r="H8" s="18">
         <f t="shared" si="0"/>
-        <v>2579.6280722494112</v>
+        <v>188.4504940011895</v>
       </c>
       <c r="I8" s="18">
         <f t="shared" si="0"/>
-        <v>2607.4715657030551</v>
+        <v>182.96164466134903</v>
       </c>
       <c r="J8" s="18">
         <f t="shared" si="0"/>
-        <v>2637.5199855509622</v>
+        <v>177.63266471975632</v>
       </c>
       <c r="K8" s="18">
         <f t="shared" si="0"/>
-        <v>2669.5709726607206</v>
+        <v>172.45889778617118</v>
       </c>
       <c r="L8" s="18">
         <f t="shared" si="0"/>
-        <v>2692.8330628056278</v>
+        <v>167.43582309337009</v>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>2715.0603144269971</v>
+        <v>162.55905154696123</v>
       </c>
       <c r="N8" s="18">
         <f t="shared" si="0"/>
@@ -12688,13 +12687,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -12789,7 +12788,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12812,89 +12811,82 @@
         <v>24444.57340361876</v>
       </c>
       <c r="G2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14*'Commercial Vehicles'!$B16</f>
-        <v>23732.59553749394</v>
+        <v>0</v>
       </c>
       <c r="H2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14*'Commercial Vehicles'!$B16</f>
-        <v>23041.354890770817</v>
+        <v>0</v>
       </c>
       <c r="I2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14*'Commercial Vehicles'!$B16</f>
-        <v>22370.247466767789</v>
+        <v>0</v>
       </c>
       <c r="J2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14*'Commercial Vehicles'!$B16</f>
-        <v>21718.686860939597</v>
+        <v>0</v>
       </c>
       <c r="K2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14*'Commercial Vehicles'!$B16</f>
-        <v>21086.103748485046</v>
+        <v>0</v>
       </c>
       <c r="L2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14*'Commercial Vehicles'!$B16</f>
-        <v>20471.945386878688</v>
+        <v>0</v>
       </c>
       <c r="M2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14*'Commercial Vehicles'!$B16</f>
-        <v>19875.675132891927</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="N2" s="51">
+        <v>0</v>
+      </c>
+      <c r="O2" s="51">
+        <v>0</v>
+      </c>
+      <c r="P2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="51">
+        <v>0</v>
+      </c>
+      <c r="R2" s="51">
+        <v>0</v>
+      </c>
+      <c r="S2" s="51">
+        <v>0</v>
+      </c>
+      <c r="T2" s="51">
+        <v>0</v>
+      </c>
+      <c r="U2" s="51">
+        <v>0</v>
+      </c>
+      <c r="V2" s="51">
+        <v>0</v>
+      </c>
+      <c r="W2" s="51">
+        <v>0</v>
+      </c>
+      <c r="X2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12989,7 +12981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13084,7 +13076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13179,7 +13171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13203,31 +13195,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>23732.59553749394</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>23041.354890770817</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>22370.247466767789</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>21718.686860939597</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>21086.103748485046</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>20471.945386878688</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>19875.675132891927</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -13284,7 +13276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -13379,7 +13371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -13403,31 +13395,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>23732.59553749394</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>23041.354890770817</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>22370.247466767789</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>21718.686860939597</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>21086.103748485046</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>20471.945386878688</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>19875.675132891927</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -13495,12 +13487,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -13595,7 +13587,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13690,7 +13682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13785,7 +13777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13880,7 +13872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13975,7 +13967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14070,7 +14062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -14165,7 +14157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -14271,12 +14263,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -14371,7 +14363,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14466,7 +14458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14561,7 +14553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14656,7 +14648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14751,7 +14743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14846,7 +14838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -14941,7 +14933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -15047,12 +15039,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -15147,7 +15139,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15242,7 +15234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15337,7 +15329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -15432,7 +15424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15527,7 +15519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15622,7 +15614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -15717,7 +15709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
